--- a/pre-week-3/homework1_exercise1A.xlsx
+++ b/pre-week-3/homework1_exercise1A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\godkn\Documents\DataAnalytics\pre-week-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC7EB9D-C3AB-4DFD-BCE2-DA04B25C0F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1A277F-E31B-41BB-944C-126527D4E345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30" yWindow="330" windowWidth="8820" windowHeight="10950" xr2:uid="{7B99AAD1-F65F-4213-9FE0-577EE026E78A}"/>
   </bookViews>
